--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.27681680876461</v>
+        <v>13.04498273142425</v>
       </c>
       <c r="D2" t="n">
-        <v>80.25152464965747</v>
+        <v>13.04087275556934</v>
       </c>
       <c r="E2" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F2" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.76412757100218</v>
+        <v>11.98667073028785</v>
       </c>
       <c r="D3" t="n">
-        <v>73.73842660784355</v>
+        <v>11.98249432377458</v>
       </c>
       <c r="E3" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F3" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.2610770677511</v>
+        <v>9.467425023509554</v>
       </c>
       <c r="D4" t="n">
-        <v>58.30718294889987</v>
+        <v>9.47491722919623</v>
       </c>
       <c r="E4" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F4" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.60440637522557</v>
+        <v>7.898216035974156</v>
       </c>
       <c r="D5" t="n">
-        <v>48.62977092276324</v>
+        <v>7.902337774949026</v>
       </c>
       <c r="E5" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F5" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.2857688612534</v>
+        <v>6.546437439953678</v>
       </c>
       <c r="D6" t="n">
-        <v>40.34480183049023</v>
+        <v>6.556030297454662</v>
       </c>
       <c r="E6" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F6" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.66795009043259</v>
+        <v>4.983541889695296</v>
       </c>
       <c r="D7" t="n">
-        <v>30.73187460243258</v>
+        <v>4.993929622895294</v>
       </c>
       <c r="E7" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F7" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.71549585931955</v>
+        <v>11.49126807713943</v>
       </c>
       <c r="D8" t="n">
-        <v>70.81551362388699</v>
+        <v>11.50752096388164</v>
       </c>
       <c r="E8" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F8" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.54514651514879</v>
+        <v>4.476086308711679</v>
       </c>
       <c r="D9" t="n">
-        <v>27.64620552817643</v>
+        <v>4.49250839832867</v>
       </c>
       <c r="E9" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F9" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.80966255000253</v>
+        <v>3.219070164375411</v>
       </c>
       <c r="D10" t="n">
-        <v>19.92116820760733</v>
+        <v>3.237189833736191</v>
       </c>
       <c r="E10" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F10" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50852079482649</v>
+        <v>3.495134629159304</v>
       </c>
       <c r="D11" t="n">
-        <v>21.61885416919106</v>
+        <v>3.513063802493547</v>
       </c>
       <c r="E11" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F11" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.9761987001167</v>
+        <v>7.958632288768964</v>
       </c>
       <c r="D12" t="n">
-        <v>48.87646845917482</v>
+        <v>7.942426124615908</v>
       </c>
       <c r="E12" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F12" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.96356048434329</v>
+        <v>6.331578578705785</v>
       </c>
       <c r="D13" t="n">
-        <v>39.0755925472401</v>
+        <v>6.349783788926517</v>
       </c>
       <c r="E13" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F13" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.26043929884472</v>
+        <v>5.079821386062267</v>
       </c>
       <c r="D14" t="n">
-        <v>31.17978932219194</v>
+        <v>5.066715764856191</v>
       </c>
       <c r="E14" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F14" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.06037693757647</v>
+        <v>6.347311252356177</v>
       </c>
       <c r="D15" t="n">
-        <v>38.97465115404963</v>
+        <v>6.333380812533066</v>
       </c>
       <c r="E15" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F15" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.85759562966229</v>
+        <v>2.739359289820122</v>
       </c>
       <c r="D16" t="n">
-        <v>16.89796429533234</v>
+        <v>2.745919197991505</v>
       </c>
       <c r="E16" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F16" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>70.6771997642639</v>
+        <v>11.48504496169289</v>
       </c>
       <c r="D17" t="n">
-        <v>70.78983117628967</v>
+        <v>11.50334756614707</v>
       </c>
       <c r="E17" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F17" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.50721852344121</v>
+        <v>4.469923010059198</v>
       </c>
       <c r="D18" t="n">
-        <v>27.60457644721321</v>
+        <v>4.485743672672147</v>
       </c>
       <c r="E18" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F18" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>55.20249193952959</v>
+        <v>8.970404940173559</v>
       </c>
       <c r="D19" t="n">
-        <v>55.12148227008891</v>
+        <v>8.957240868889448</v>
       </c>
       <c r="E19" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F19" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>30.70257865294595</v>
+        <v>4.989169031103717</v>
       </c>
       <c r="D20" t="n">
-        <v>30.76796138449068</v>
+        <v>4.999793724979735</v>
       </c>
       <c r="E20" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F20" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>35.74030829983276</v>
+        <v>5.807800098722824</v>
       </c>
       <c r="D21" t="n">
-        <v>35.69431011507343</v>
+        <v>5.800325393699432</v>
       </c>
       <c r="E21" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F21" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>10.71646193182917</v>
+        <v>1.74142506392224</v>
       </c>
       <c r="D22" t="n">
-        <v>10.69175477309596</v>
+        <v>1.737410150628093</v>
       </c>
       <c r="E22" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F22" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>47.25954334592555</v>
+        <v>7.679675793712902</v>
       </c>
       <c r="D23" t="n">
-        <v>47.22003692193363</v>
+        <v>7.673255999814215</v>
       </c>
       <c r="E23" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F23" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>50.90474743929069</v>
+        <v>8.272021458884737</v>
       </c>
       <c r="D24" t="n">
-        <v>50.89528696277192</v>
+        <v>8.270484131450438</v>
       </c>
       <c r="E24" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F24" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>75.32252357047987</v>
+        <v>12.23991008020298</v>
       </c>
       <c r="D25" t="n">
-        <v>75.2597122584091</v>
+        <v>12.22970324199148</v>
       </c>
       <c r="E25" t="n">
-        <v>19.54405498931068</v>
+        <v>3.175908935762985</v>
       </c>
       <c r="F25" t="n">
-        <v>19.52694106649465</v>
+        <v>3.173127923305381</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
